--- a/report_forms/033_pci_preparation_and_outcome_log--report_forms.xlsx
+++ b/report_forms/033_pci_preparation_and_outcome_log--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>submitted_on</t>
+          <t>submitted_on_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>submittedon</t>
+          <t>Submitted On 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>pcioutcome</t>
+          <t>Pci Outcome</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Comments 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>cath_lab_info</t>
+          <t>cath_lab_info_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>cathlabinfo</t>
+          <t>Cath Lab Info 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>cardiology_team</t>
+          <t>cardiology_team_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>cardiolteam</t>
+          <t>Cardiology Team 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>cardiology_physician</t>
+          <t>cardiology_physician_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>cardiolphys</t>
+          <t>Cardiology Physician 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1032,7 +1032,7 @@
   <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1244,7 +1244,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cardiology_team_choices</t>
+          <t>cardiology_team_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cardiology_team_choices</t>
+          <t>cardiology_team_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1278,7 +1278,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cardiology_physician_choices</t>
+          <t>cardiology_physician_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cardiology_physician_choices</t>
+          <t>cardiology_physician_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
